--- a/data/trans_bre/P5_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P5_R-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,62; 12,86</t>
+          <t>-9,84; 13,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-19,94; 6,48</t>
+          <t>-20,15; 8,1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,85; 14,0</t>
+          <t>-11,94; 14,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,6; 10,88</t>
+          <t>-8,12; 10,79</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-32,7; 66,82</t>
+          <t>-30,45; 71,61</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-40,57; 17,92</t>
+          <t>-41,05; 22,4</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-26,83; 42,18</t>
+          <t>-27,14; 45,5</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-35,05; 78,46</t>
+          <t>-36,6; 79,81</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-12,74; 8,64</t>
+          <t>-13,15; 9,09</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-22,36; 5,13</t>
+          <t>-21,8; 6,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-9,54; 12,5</t>
+          <t>-9,64; 13,54</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-7,12; 11,47</t>
+          <t>-7,98; 10,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-50,95; 65,3</t>
+          <t>-52,47; 66,3</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-42,32; 13,66</t>
+          <t>-42,13; 16,12</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-25,07; 42,29</t>
+          <t>-24,94; 46,97</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-35,52; 105,32</t>
+          <t>-37,78; 89,57</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-21,17; 2,54</t>
+          <t>-22,32; 1,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-16,15; 10,3</t>
+          <t>-16,71; 10,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-15,74; 13,51</t>
+          <t>-16,17; 13,43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 21,22</t>
+          <t>-1,98; 20,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-61,41; 11,99</t>
+          <t>-62,64; 6,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-39,65; 41,97</t>
+          <t>-41,08; 38,41</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-38,87; 47,71</t>
+          <t>-39,31; 50,22</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-22,95; 305,27</t>
+          <t>-16,41; 297,42</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 12,71</t>
+          <t>-3,56; 12,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,14; 19,06</t>
+          <t>0,02; 19,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-14,5; 2,71</t>
+          <t>-15,24; 2,34</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,94; 32,44</t>
+          <t>-6,01; 31,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-9,88; 52,78</t>
+          <t>-10,93; 55,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 63,18</t>
+          <t>-0,66; 64,85</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-33,87; 8,71</t>
+          <t>-35,36; 7,28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-30,21; 235,29</t>
+          <t>-31,31; 204,39</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-13,77; 11,12</t>
+          <t>-13,58; 10,7</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-16,06; 7,56</t>
+          <t>-16,04; 7,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-16,65; 5,59</t>
+          <t>-16,44; 6,16</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,18; 17,35</t>
+          <t>-0,13; 16,82</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-35,9; 40,32</t>
+          <t>-35,07; 37,44</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-40,57; 26,58</t>
+          <t>-39,15; 27,98</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-36,29; 17,3</t>
+          <t>-37,11; 18,23</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,93; 131,69</t>
+          <t>-0,92; 138,27</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-8,36; 15,8</t>
+          <t>-9,19; 14,37</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-13,03; 17,29</t>
+          <t>-11,7; 16,9</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-13,44; 14,53</t>
+          <t>-14,6; 14,47</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-16,78; 3,81</t>
+          <t>-16,55; 3,67</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-26,54; 75,1</t>
+          <t>-28,72; 73,08</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-26,38; 46,03</t>
+          <t>-23,26; 45,69</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-30,1; 45,79</t>
+          <t>-31,16; 45,46</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-68,88; 31,9</t>
+          <t>-68,42; 33,31</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 4,55</t>
+          <t>-4,41; 4,59</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 5,01</t>
+          <t>-5,48; 4,76</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,06; 2,81</t>
+          <t>-6,68; 2,29</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 14,37</t>
+          <t>-0,65; 16,36</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-14,68; 17,58</t>
+          <t>-14,88; 17,75</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-13,32; 13,84</t>
+          <t>-13,2; 13,47</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-17,8; 7,93</t>
+          <t>-16,93; 6,49</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 88,56</t>
+          <t>-3,63; 99,32</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P5_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P5_R-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,84; 13,31</t>
+          <t>-9,21; 13,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-20,15; 8,1</t>
+          <t>-19,3; 7,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,94; 14,82</t>
+          <t>-11,8; 14,4</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,12; 10,79</t>
+          <t>-7,1; 10,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-30,45; 71,61</t>
+          <t>-30,22; 66,58</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-41,05; 22,4</t>
+          <t>-39,03; 20,7</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-27,14; 45,5</t>
+          <t>-26,69; 45,37</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-36,6; 79,81</t>
+          <t>-32,46; 73,68</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-13,15; 9,09</t>
+          <t>-13,62; 8,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-21,8; 6,16</t>
+          <t>-21,28; 5,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-9,64; 13,54</t>
+          <t>-10,14; 12,16</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-7,98; 10,43</t>
+          <t>-8,16; 10,83</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-52,47; 66,3</t>
+          <t>-52,63; 55,32</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-42,13; 16,12</t>
+          <t>-43,41; 14,52</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-24,94; 46,97</t>
+          <t>-26,64; 44,53</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-37,78; 89,57</t>
+          <t>-37,08; 92,94</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-22,32; 1,41</t>
+          <t>-23,08; 0,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-16,71; 10,12</t>
+          <t>-15,37; 12,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-16,17; 13,43</t>
+          <t>-14,93; 14,18</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 20,86</t>
+          <t>-2,39; 20,66</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-62,64; 6,37</t>
+          <t>-63,15; 4,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-41,08; 38,41</t>
+          <t>-37,35; 44,62</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-39,31; 50,22</t>
+          <t>-36,01; 51,77</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-16,41; 297,42</t>
+          <t>-23,62; 296,33</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 12,96</t>
+          <t>-3,6; 13,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,02; 19,25</t>
+          <t>1,05; 20,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-15,24; 2,34</t>
+          <t>-14,04; 2,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,01; 31,28</t>
+          <t>-6,87; 31,29</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-10,93; 55,05</t>
+          <t>-12,08; 57,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 64,85</t>
+          <t>2,63; 68,09</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-35,36; 7,28</t>
+          <t>-33,54; 7,92</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-31,31; 204,39</t>
+          <t>-34,84; 194,72</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-13,58; 10,7</t>
+          <t>-13,48; 11,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-16,04; 7,71</t>
+          <t>-16,67; 6,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-16,44; 6,16</t>
+          <t>-15,96; 5,72</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 16,82</t>
+          <t>0,17; 17,52</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-35,07; 37,44</t>
+          <t>-35,31; 38,05</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-39,15; 27,98</t>
+          <t>-40,67; 23,83</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-37,11; 18,23</t>
+          <t>-36,73; 16,87</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 138,27</t>
+          <t>0,3; 138,41</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-9,19; 14,37</t>
+          <t>-8,08; 15,23</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-11,7; 16,9</t>
+          <t>-12,96; 16,89</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-14,6; 14,47</t>
+          <t>-13,35; 15,16</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-16,55; 3,67</t>
+          <t>-17,25; 4,18</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-28,72; 73,08</t>
+          <t>-24,87; 67,6</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-23,26; 45,69</t>
+          <t>-26,27; 44,62</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-31,16; 45,46</t>
+          <t>-30,19; 49,15</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-68,42; 33,31</t>
+          <t>-70,16; 37,86</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 4,59</t>
+          <t>-4,16; 4,19</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 4,76</t>
+          <t>-4,87; 4,89</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,68; 2,29</t>
+          <t>-7,29; 2,13</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 16,36</t>
+          <t>-0,57; 15,1</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-14,88; 17,75</t>
+          <t>-13,57; 16,15</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-13,2; 13,47</t>
+          <t>-12,01; 13,52</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-16,93; 6,49</t>
+          <t>-18,28; 5,86</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 99,32</t>
+          <t>-3,78; 96,0</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P5_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P5_R-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,61</t>
+          <t>0,94</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,21; 13,43</t>
+          <t>-10,62; 12,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-19,3; 7,49</t>
+          <t>-19,94; 6,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,8; 14,4</t>
+          <t>-11,85; 14,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,1; 10,14</t>
+          <t>-8,69; 10,49</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-30,22; 66,58</t>
+          <t>-32,7; 66,82</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-39,03; 20,7</t>
+          <t>-40,57; 17,92</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-26,69; 45,37</t>
+          <t>-26,83; 42,18</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-32,46; 73,68</t>
+          <t>-36,48; 75,63</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,35</t>
+          <t>1,3</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>7,95%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-13,62; 8,13</t>
+          <t>-12,74; 8,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-21,28; 5,46</t>
+          <t>-22,36; 5,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-10,14; 12,16</t>
+          <t>-9,54; 12,5</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-8,16; 10,83</t>
+          <t>-7,33; 11,37</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-52,63; 55,32</t>
+          <t>-50,95; 65,3</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-43,41; 14,52</t>
+          <t>-42,32; 13,66</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-26,64; 44,53</t>
+          <t>-25,07; 42,29</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-37,08; 92,94</t>
+          <t>-37,29; 104,26</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8,73</t>
+          <t>7,65</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>78,47%</t>
+          <t>65,15%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-23,08; 0,85</t>
+          <t>-21,17; 2,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-15,37; 12,1</t>
+          <t>-16,15; 10,3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,93; 14,18</t>
+          <t>-15,74; 13,51</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 20,66</t>
+          <t>-4,17; 20,13</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-63,15; 4,17</t>
+          <t>-61,41; 11,99</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-37,35; 44,62</t>
+          <t>-39,65; 41,97</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-36,01; 51,77</t>
+          <t>-38,87; 47,71</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-23,62; 296,33</t>
+          <t>-26,92; 306,71</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6,62</t>
+          <t>-2,44</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>-12,9%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 13,22</t>
+          <t>-3,0; 12,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,05; 20,2</t>
+          <t>0,14; 19,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-14,04; 2,61</t>
+          <t>-14,5; 2,71</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,87; 31,29</t>
+          <t>-8,93; 4,94</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-12,08; 57,97</t>
+          <t>-9,88; 52,78</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,63; 68,09</t>
+          <t>0,35; 63,18</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-33,54; 7,92</t>
+          <t>-33,87; 8,71</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-34,84; 194,72</t>
+          <t>-40,45; 34,43</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8,29</t>
+          <t>8,94</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>49,31%</t>
+          <t>52,65%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-13,48; 11,19</t>
+          <t>-13,77; 11,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-16,67; 6,72</t>
+          <t>-16,06; 7,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-15,96; 5,72</t>
+          <t>-16,65; 5,59</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,17; 17,52</t>
+          <t>0,44; 17,63</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-35,31; 38,05</t>
+          <t>-35,9; 40,32</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-40,67; 23,83</t>
+          <t>-40,57; 26,58</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-36,73; 16,87</t>
+          <t>-36,29; 17,3</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,3; 138,41</t>
+          <t>2,76; 140,59</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-6,29</t>
+          <t>-7,24</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-34,0%</t>
+          <t>-39,27%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-8,08; 15,23</t>
+          <t>-8,36; 15,8</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-12,96; 16,89</t>
+          <t>-13,03; 17,29</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-13,35; 15,16</t>
+          <t>-13,44; 14,53</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-17,25; 4,18</t>
+          <t>-17,63; 2,52</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-24,87; 67,6</t>
+          <t>-26,54; 75,1</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-26,27; 44,62</t>
+          <t>-26,38; 46,03</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-30,19; 49,15</t>
+          <t>-30,1; 45,79</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-70,16; 37,86</t>
+          <t>-72,45; 22,49</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4,29</t>
+          <t>1,17</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>6,69%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 4,19</t>
+          <t>-4,4; 4,55</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 4,89</t>
+          <t>-5,42; 5,01</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,29; 2,13</t>
+          <t>-7,06; 2,81</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 15,1</t>
+          <t>-2,36; 4,89</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-13,57; 16,15</t>
+          <t>-14,68; 17,58</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-12,01; 13,52</t>
+          <t>-13,32; 13,84</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-18,28; 5,86</t>
+          <t>-17,8; 7,93</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 96,0</t>
+          <t>-12,59; 30,32</t>
         </is>
       </c>
     </row>
